--- a/registers/Provenance_Register.xlsx
+++ b/registers/Provenance_Register.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -526,20 +526,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R-BUILD-2045-FE-LP</t>
+          <t>R-ACCREDIT-2030</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Iron-air energy, 2045 LP solve</t>
+          <t>Na-ion own-data capacity credit, 2030 checkpoint, no-foresight dispatch</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3635866.8</v>
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MWh</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2045</v>
+        <v>2030</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -557,18 +557,23 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>R-BUILD-2045-FE-UPLIFT</t>
+          <t>pending re-solve on corrected demand</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>(not retained -- result discarded)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>A-FE-DURATION, A-FE-CAPEX</t>
+          <t>A-CHECKPOINT-CSV-VINTAGE</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Failed 8-year cross-test in design year 2016-17 (470,502 MWh unserved)</t>
+          <t>DISCARDED, not merely uncertain. Computed 0.0% but rests on the superseded demand vintage, so the peak net-demand hours identified are the wrong hours -- correcting the separate iron-air omission would not fix this. Also credited Na-ion only, omitting long-duration storage present at 2035 (116,127 MWh), which biases credit downward. BLOCKED pending a re-solve of these checkpoints on corrected demand.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -580,20 +585,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R-BUILD-2045-FE-UPLIFT</t>
+          <t>R-ACCREDIT-2035</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Iron-air energy, 2045, +20% uplift after 8-year cross-test</t>
+          <t>Na-ion own-data capacity credit, 2035 checkpoint, no-foresight dispatch</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4363040.2</v>
+        <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MWh</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -602,27 +607,32 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2045</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>provisional</t>
+        <v>2035</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>superseded</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>pending re-solve on corrected demand</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>sim_2045_uplift.py</t>
+          <t>(not retained -- result discarded)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>A-FE-DURATION, A-FE-CAPEX</t>
+          <t>A-CHECKPOINT-CSV-VINTAGE</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Manual sweep, not optimization -- cheapest technology to close the gap was never tested. Sized partly against heuristic-dispatch shortfall, not purely physical.</t>
+          <t>DISCARDED, not merely uncertain. Computed 0.0% but rests on the superseded demand vintage, so the peak net-demand hours identified are the wrong hours -- correcting the separate iron-air omission would not fix this. Also credited Na-ion only, omitting long-duration storage present at 2035 (116,127 MWh), which biases credit downward. BLOCKED pending a re-solve of these checkpoints on corrected demand.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -634,20 +644,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R-BUILD-2045-SOLAR</t>
+          <t>R-ACCREDIT-2040</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Total solar, 2045 checkpoint (166,340.7 utility + 7,440 distributed)</t>
+          <t>Na-ion own-data capacity credit, 2040 checkpoint, no-foresight dispatch</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>173780.7</v>
+        <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -656,27 +666,32 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2045</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>provisional</t>
+        <v>2040</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>superseded</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>pending re-solve on corrected demand</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>solve_2045_v3.py</t>
+          <t>(not retained -- result discarded)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>A-SITING-CAP-DOM, A-DEMAND-2045</t>
+          <t>A-CHECKPOINT-CSV-VINTAGE</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Single design weather year 2016-17; distributed solar pinned at siting cap</t>
+          <t>DISCARDED, not merely uncertain. Computed 0.0% but rests on the superseded demand vintage, so the peak net-demand hours identified are the wrong hours -- correcting the separate iron-air omission would not fix this. Also credited Na-ion only, omitting long-duration storage present at 2035 (116,127 MWh), which biases credit downward. BLOCKED pending a re-solve of these checkpoints on corrected demand.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -688,39 +703,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-DOMINION-IRP-NPV</t>
+          <t>R-ACCREDIT-2045</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dominion 2025 IRP Company Preferred Plan, Total Plan NPV</t>
+          <t>Na-ion own-data capacity credit, 2045, no-foresight 8-year dispatch</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>148.7</v>
+        <v>0.318</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$B</t>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>S1</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>2045</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>current</t>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>scripts/sim_2045_8yr.py + lp_package/storage_accreditation.py</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>A-STORAGE-MANDATE-2045</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Case PUR-2025-00184, 2026-2045, 6.62% discount rate. Includes only 2,000 MW storage -- predates HB895/SB448 requiring 19,480 MW.</t>
+          <t>STANDS. Derived from this session own 8-year heuristic simulation using corrected (2B-1 basis) demand and a fleet from this session own solve -- NOT from the superseded checkpoint CSVs. Below PJM published 50% for 4-hour storage, so the A.13 cross-validation rule adopts it. Provisional because it credits Na-ion only and rests on a single heuristic dispatch policy; a more anticipatory policy would raise it.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -732,21 +753,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R-FIRMING-PCT</t>
+          <t>R-BUILD-2045-FE-LP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Six-day lookahead firming percentage, NoVA fleet</t>
+          <t>Iron-air energy, 2045 LP solve</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.3</v>
+        <v>3635866.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>percent</t>
-        </is>
+          <t>MWh</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2045</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -755,18 +784,18 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>R-BUILD-2045-FE-UPLIFT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R-NOVA-TOTAL-V1</t>
+          <t>A-FE-DURATION, A-FE-CAPEX</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>STALE: computed on the 6,159 MW fleet basis, now revised to 4,638.6 MW. Needs recomputation.</t>
+          <t>Failed 8-year cross-test in design year 2016-17 (470,502 MWh unserved)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -778,37 +807,49 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R-NOVA-TOTAL-V1</t>
+          <t>R-BUILD-2045-FE-UPLIFT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Four-county NoVA distributed solar potential (original)</t>
+          <t>Iron-air energy, 2045, +20% uplift after 8-year cross-test</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6159</v>
+        <v>4363040.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>superseded</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>R-NOVA-TOTAL-V2</t>
+          <t>MWh</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2045</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>sim_2045_uplift.py</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>A-FE-DURATION, A-FE-CAPEX</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>PWC parking population-anchored; inflated by Loudoun data-center density</t>
+          <t>Manual sweep, not optimization -- cheapest technology to close the gap was never tested. Sized partly against heuristic-dispatch shortfall, not purely physical.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -820,31 +861,49 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R-NOVA-TOTAL-V2</t>
+          <t>R-BUILD-2045-SOLAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Four-county NoVA distributed solar potential, PWC re-based</t>
+          <t>Total solar, 2045 checkpoint (166,340.7 utility + 7,440 distributed)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4638.6</v>
+        <v>173780.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>MW</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>current</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2045</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>solve_2045_v3.py</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>A-PWC-PARKING-V2</t>
+          <t>A-SITING-CAP-DOM, A-DEMAND-2045</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Single design weather year 2016-17; distributed solar pinned at siting cap</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -856,29 +915,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R-SLCOE-S1-2030</t>
+          <t>R-DOMINION-IRP-NPV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Scenario 1 SLCOE 2030, Python pipeline with reserve margin</t>
+          <t>Dominion 2025 IRP Company Preferred Plan, Total Plan NPV</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>42.45</v>
+        <v>148.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$/MWh</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>S1</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2030</v>
+        <v>2045</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
@@ -886,7 +940,16 @@
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>A-STORAGE-MANDATE-2045</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Case PUR-2025-00184, 2026-2045, 6.62% discount rate. Includes only 2,000 MW storage -- predates HB895/SB448 requiring 19,480 MW.</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -896,44 +959,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R-SLCOE-S1-2045</t>
+          <t>R-FIRMING-PCT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Scenario 1 SLCOE 2045 at +20% iron-air uplift</t>
+          <t>Six-day lookahead firming percentage, NoVA fleet</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>133.5</v>
+        <v>4.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$/MWh</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>2045</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>provisional</t>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>superseded</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>R-BUILD-2045-SOLAR, R-BUILD-2045-FE-UPLIFT</t>
+          <t>R-NOVA-TOTAL-V1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No technology cost-decline curve applied; likely conservative</t>
+          <t>STALE: computed on the 6,159 MW fleet basis, now revised to 4,638.6 MW. Needs recomputation.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -945,48 +1005,269 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R-UNSERVED-2030-8YR</t>
+          <t>R-NOVA-TOTAL-V1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8-year continuous dispatch unserved energy, 2030 build</t>
+          <t>Four-county NoVA distributed solar potential (original)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6444435.4</v>
+        <v>6159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MWh</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2030</v>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>simulate_8yr_dispatch.py</t>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>superseded</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>R-NOVA-TOTAL-V2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
+          <t>PWC parking population-anchored; inflated by Loudoun data-center density</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R-NOVA-TOTAL-V2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Four-county NoVA distributed solar potential, PWC re-based</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4638.6</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>A-PWC-PARKING-V2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R-S2-GAS-CAPACITY-RANGE-2045</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Statutory Floor gas capacity requirement, 2045, range across storage accreditation bases</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>20200</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2045</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>scripts/compare_scenario2_capacity_standards.py</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R-ACCREDIT-2045</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Range: 4,485 MW at nameplate credit, ~20,200 MW at the 31.8% no-foresight credit, 22,446 MW at zero credit (Appendix C.2 rule). The 18 GW spread is entirely the storage accreditation assumption. Point value recorded is the derived conservative case.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R-SLCOE-S1-2030</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Scenario 1 SLCOE 2030, Python pipeline with reserve margin</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>$/MWh</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2030</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>R-SLCOE-S1-2045</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Scenario 1 SLCOE 2045 at +20% iron-air uplift</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>$/MWh</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2045</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R-BUILD-2045-SOLAR, R-BUILD-2045-FE-UPLIFT</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>No technology cost-decline curve applied; likely conservative</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R-UNSERVED-2030-8YR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>8-year continuous dispatch unserved energy, 2030 build</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6444435.4</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MWh</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2030</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>simulate_8yr_dispatch.py</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>Storage charge-starved: already captures 75.4% of all available surplus</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
@@ -1003,7 +1284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1055,20 +1336,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A-DEMAND-2045</t>
+          <t>A-CHECKPOINT-CSV-VINTAGE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DOM zone 2045 annual demand, April-March fiscal year</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>206.3</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TWh</t>
+          <t>The four VA_YYYY_Scenario1_hourly CSVs in results/hourly_dispatch/ rest on the SUPERSEDED demand vintage (Internal Debugging Log #24). 2030 shows 144.1 TWh / 19,038 MW peak against the current sourced 110,864 GWh. Trajectory 144.1-&gt;176.7 TWh (+23%) versus the current 2B-1 series 110,864-&gt;186,462 GWh (+68%): wrong level AND wrong growth shape. The 2045 file also uses a different 17-column schema (net rather than separate charge/discharge), indicating a different code vintage.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>superseded demand basis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -1081,20 +1359,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A-DIST-STORAGE-PAIR</t>
+          <t>A-DEMAND-2045</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Distributed storage pairing: 1:1 MW with distributed solar, 4-hour duration</t>
+          <t>DOM zone 2045 annual demand, April-March fiscal year</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>206.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>hours</t>
+          <t>TWh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -1107,20 +1385,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A-FE-CAPEX</t>
+          <t>A-DIST-STORAGE-PAIR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Iron-air energy capex</t>
+          <t>Distributed storage pairing: 1:1 MW with distributed solar, 4-hour duration</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.03</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$/kWh</t>
+          <t>hours</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -1133,25 +1411,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A-FE-DURATION</t>
+          <t>A-FE-CAPEX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Iron-air duration (power = energy/100)</t>
+          <t>Iron-air energy capex</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>100</v>
+        <v>18.03</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>hours</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>C122</t>
+          <t>$/kWh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -1164,20 +1437,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A-NA-CAPEX-ENERGY</t>
+          <t>A-FE-DURATION</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sodium-ion energy capex</t>
+          <t>Iron-air duration (power = energy/100)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>65.16</v>
+        <v>100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$/kWh</t>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C122</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -1190,20 +1468,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A-PWC-PARKING-V2</t>
+          <t>A-NA-CAPEX-ENERGY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PWC parking-lot solar, re-anchored to C&amp;I building footprint (population anchor imported Loudoun data-center distortion)</t>
+          <t>Sodium-ion energy capex</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>335.6</v>
+        <v>65.16</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>$/kWh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1216,16 +1494,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A-SITING-CAP-DOM</t>
+          <t>A-PWC-PARKING-V2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Distributed solar siting cap, DOM zone, extrapolated from re-based four-county NoVA at 0.93 kW/capita excluding Loudoun</t>
+          <t>PWC parking-lot solar, re-anchored to C&amp;I building footprint (population anchor imported Loudoun data-center distortion)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7440</v>
+        <v>335.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1242,16 +1520,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A-STORAGE-MANDATE-2045</t>
+          <t>A-SITING-CAP-DOM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dominion storage mandate under HB895/SB448: 16,000 MW short-duration + 3,480 MW LDES by 2045</t>
+          <t>Distributed solar siting cap, DOM zone, extrapolated from re-based four-county NoVA at 0.93 kW/capita excluding Loudoun</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19480</v>
+        <v>7440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1260,6 +1538,32 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A-STORAGE-MANDATE-2045</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dominion storage mandate under HB895/SB448: 16,000 MW short-duration + 3,480 MW LDES by 2045</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>19480</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
@@ -1289,9 +1593,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -1299,9 +1601,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -1330,9 +1630,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -1354,9 +1652,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -1378,9 +1674,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
